--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348963</v>
+        <v>120348951</v>
       </c>
       <c r="B3" t="n">
-        <v>57240</v>
+        <v>57218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,30 +819,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102110</v>
+        <v>100034</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -901,11 +909,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348956</v>
+        <v>120348987</v>
       </c>
       <c r="B4" t="n">
-        <v>57202</v>
+        <v>57996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,20 +947,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,14 +970,10 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348959</v>
+        <v>120348981</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>58027</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1075,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102611</v>
+        <v>103057</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1099,11 +1098,7 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1188,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348951</v>
+        <v>120348956</v>
       </c>
       <c r="B6" t="n">
-        <v>57218</v>
+        <v>57202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100034</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1228,14 +1223,10 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1320,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348981</v>
+        <v>120348963</v>
       </c>
       <c r="B7" t="n">
-        <v>58027</v>
+        <v>57240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,26 +1327,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103057</v>
+        <v>102110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1418,6 +1409,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,10 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348987</v>
+        <v>120348959</v>
       </c>
       <c r="B8" t="n">
-        <v>57996</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,34 +1452,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>102611</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348973</v>
+        <v>120348981</v>
       </c>
       <c r="B2" t="n">
-        <v>56373</v>
+        <v>58027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100045</v>
+        <v>103057</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +710,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -803,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348951</v>
+        <v>120348959</v>
       </c>
       <c r="B3" t="n">
-        <v>57218</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100034</v>
+        <v>102611</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,14 +837,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -935,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348987</v>
+        <v>120348956</v>
       </c>
       <c r="B4" t="n">
-        <v>57996</v>
+        <v>57202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,20 +939,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100011</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,10 +962,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348981</v>
+        <v>120348963</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>57240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,26 +1071,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103057</v>
+        <v>102110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1157,6 +1153,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348956</v>
+        <v>120348951</v>
       </c>
       <c r="B6" t="n">
-        <v>57202</v>
+        <v>57218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,21 +1200,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100011</v>
+        <v>100034</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1223,10 +1224,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348963</v>
+        <v>120348973</v>
       </c>
       <c r="B7" t="n">
-        <v>57240</v>
+        <v>56373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,33 +1328,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102110</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1409,11 +1418,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,10 +1444,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348959</v>
+        <v>120348987</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,38 +1456,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102611</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348981</v>
+        <v>120348951</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>57218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103057</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,8 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -799,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348959</v>
+        <v>120348956</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102611</v>
+        <v>100011</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,12 +845,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -927,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348956</v>
+        <v>120348959</v>
       </c>
       <c r="B4" t="n">
-        <v>57202</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>102611</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,12 +973,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1184,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348951</v>
+        <v>120348987</v>
       </c>
       <c r="B6" t="n">
-        <v>57218</v>
+        <v>57996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,42 +1204,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100034</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348987</v>
+        <v>120348981</v>
       </c>
       <c r="B8" t="n">
-        <v>57996</v>
+        <v>58027</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,20 +1456,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103057</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348951</v>
+        <v>120348963</v>
       </c>
       <c r="B2" t="n">
-        <v>57218</v>
+        <v>57240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100034</v>
+        <v>102110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -781,6 +773,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -935,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348959</v>
+        <v>120348981</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>58027</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +948,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102611</v>
+        <v>103057</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,11 +971,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1063,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348963</v>
+        <v>120348959</v>
       </c>
       <c r="B5" t="n">
-        <v>57240</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,30 +1072,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102110</v>
+        <v>102611</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1161,11 +1158,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1444,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348981</v>
+        <v>120348951</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>57218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,21 +1452,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103057</v>
+        <v>100034</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1482,8 +1474,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348956</v>
+        <v>120348951</v>
       </c>
       <c r="B3" t="n">
-        <v>57202</v>
+        <v>57218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100011</v>
+        <v>100034</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +844,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -932,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348981</v>
+        <v>120348973</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>56373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,20 +948,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103057</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,10 +971,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -1308,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348973</v>
+        <v>120348981</v>
       </c>
       <c r="B7" t="n">
-        <v>56373</v>
+        <v>58027</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,20 +1328,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>103057</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1343,14 +1351,10 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1436,10 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348951</v>
+        <v>120348956</v>
       </c>
       <c r="B8" t="n">
-        <v>57218</v>
+        <v>57202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,21 +1456,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100034</v>
+        <v>100011</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1476,14 +1480,10 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348963</v>
+        <v>120348956</v>
       </c>
       <c r="B2" t="n">
-        <v>57240</v>
+        <v>57202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102110</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -773,11 +777,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348951</v>
+        <v>120348987</v>
       </c>
       <c r="B3" t="n">
-        <v>57218</v>
+        <v>57996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,42 +815,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100034</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -936,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348973</v>
+        <v>120348959</v>
       </c>
       <c r="B4" t="n">
-        <v>56373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,38 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>102611</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1064,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348959</v>
+        <v>120348963</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,34 +1071,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102611</v>
+        <v>102110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1166,6 +1153,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348987</v>
+        <v>120348981</v>
       </c>
       <c r="B6" t="n">
-        <v>57996</v>
+        <v>58027</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,20 +1196,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103057</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1227,7 +1219,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1316,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348981</v>
+        <v>120348973</v>
       </c>
       <c r="B7" t="n">
-        <v>58027</v>
+        <v>56373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,20 +1320,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103057</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1351,10 +1343,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1440,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348956</v>
+        <v>120348951</v>
       </c>
       <c r="B8" t="n">
-        <v>57202</v>
+        <v>57218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,21 +1452,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100011</v>
+        <v>100034</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1480,10 +1476,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>

--- a/artfynd/A 27655-2019 artfynd.xlsx
+++ b/artfynd/A 27655-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348956</v>
+        <v>120348981</v>
       </c>
       <c r="B2" t="n">
-        <v>57202</v>
+        <v>58027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100011</v>
+        <v>103057</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348963</v>
+        <v>120348956</v>
       </c>
       <c r="B5" t="n">
-        <v>57240</v>
+        <v>57202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,29 +1067,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102110</v>
+        <v>100011</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
@@ -1153,11 +1153,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348981</v>
+        <v>120348951</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>57218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,21 +1195,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103057</v>
+        <v>100034</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1222,8 +1217,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3K+</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1436,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348951</v>
+        <v>120348963</v>
       </c>
       <c r="B8" t="n">
-        <v>57218</v>
+        <v>57240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,38 +1455,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100034</v>
+        <v>102110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>sträckande S</t>
@@ -1542,6 +1537,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>mot SSO</t>
         </is>
       </c>
       <c r="AD8" t="b">
